--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1468,6 +1478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1616,6 +1631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2160,6 +2180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2704,6 +2729,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2852,6 +2882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3000,6 +3035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3148,6 +3188,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3692,6 +3737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3840,6 +3890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4384,6 +4439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4928,6 +4988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5076,6 +5141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5620,6 +5690,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6164,6 +6239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6312,6 +6392,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6856,6 +6941,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7400,6 +7490,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7944,6 +8039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8092,6 +8192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8636,6 +8741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8784,6 +8894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8932,6 +9047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9476,6 +9596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9624,6 +9749,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9772,6 +9902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10316,6 +10451,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10464,6 +10604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11008,6 +11153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11552,6 +11702,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11700,6 +11855,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12244,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12788,6 +12953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13332,6 +13502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13874,6 +14049,11 @@
       <c r="S77" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20768,7 +20768,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21164,7 +21164,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">

--- a/diseases/d071/2005-2009.xlsx
+++ b/diseases/d071/2005-2009.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +941,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1194,6 +1224,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1206,12 +1241,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1332,6 +1377,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1344,12 +1394,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1617,6 +1677,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1629,12 +1694,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1902,6 +1977,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1914,12 +1994,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2040,6 +2130,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2052,12 +2147,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2178,6 +2283,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2190,12 +2300,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2316,6 +2436,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2328,12 +2453,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2601,6 +2736,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2613,12 +2753,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2739,6 +2889,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2751,12 +2906,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3024,6 +3189,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3036,12 +3206,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3309,6 +3489,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3321,12 +3506,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3447,6 +3642,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3459,12 +3659,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3732,6 +3942,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3744,12 +3959,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4017,6 +4242,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4029,12 +4259,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4155,6 +4395,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4167,12 +4412,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4440,6 +4695,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4452,12 +4712,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4725,6 +4995,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4737,12 +5012,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5010,6 +5295,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5022,12 +5312,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5148,6 +5448,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5160,12 +5465,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5433,6 +5748,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5445,12 +5765,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5571,6 +5901,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5583,12 +5918,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5709,6 +6054,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5721,12 +6071,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5994,6 +6354,11 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6006,12 +6371,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6132,6 +6507,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6144,12 +6524,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6270,6 +6660,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6282,12 +6677,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6555,6 +6960,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6567,12 +6977,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6693,6 +7113,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6705,12 +7130,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6978,6 +7413,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6990,12 +7430,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7263,6 +7713,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7275,12 +7730,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7401,6 +7866,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7413,12 +7883,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7686,6 +8166,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7698,12 +8183,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7971,6 +8466,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7983,12 +8483,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8256,6 +8766,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8268,12 +8783,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8541,6 +9066,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8553,12 +9083,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
